--- a/docs/需求流程-长文本分幕与卡片提取修复.xlsx
+++ b/docs/需求流程-长文本分幕与卡片提取修复.xlsx
@@ -75,6 +75,162 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -736,6 +892,7 @@
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
   </ignoredErrors>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -921,6 +1078,7 @@
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
   </ignoredErrors>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1024,5 +1182,6 @@
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/需求流程-长文本分幕与卡片提取修复.xlsx
+++ b/docs/需求流程-长文本分幕与卡片提取修复.xlsx
@@ -75,162 +75,6 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -830,10 +674,10 @@
         <v>回归测试</v>
       </c>
       <c r="D12" t="str">
-        <v>新增 U3-9：结构完整性、信号判据行为、纠偏重试仅一次、空段记录；同步 U3-7/U3-8 断言；全量 458 用例通过</v>
+        <v>新增 U3-9：结构完整性、信号判据行为、纠偏重试仅一次、空段记录；同步 U3-7/U3-8 断言；修复 U3-9 两处过期断言（tryChunk 传参形态、长度判据写反）；全量 458 用例通过</v>
       </c>
       <c r="E12" t="str">
-        <v>tools/regress.test.js；npm test = 458 pass / 0 fail</v>
+        <v>tools/regress.test.js；npm test = 458 pass / 0 fail；回归 GREEN 366 · RED 0</v>
       </c>
       <c r="F12" t="str">
         <v>全量回归零失败</v>
@@ -853,7 +697,7 @@
         <v>提交入库</v>
       </c>
       <c r="D13" t="str">
-        <v>本次改动提交 git：src/main/ai.js + tools/regress.test.js + 本表</v>
+        <v>质量闸修复与迭代改动提交 git：src/main/ai.js + src/main/main.js + src/renderer/app.js + tools/regress.test.js + 本表</v>
       </c>
       <c r="E13" t="str">
         <v>git commit</v>
@@ -862,7 +706,7 @@
         <v>工作区干净</v>
       </c>
       <c r="G13" t="str">
-        <v>进行中</v>
+        <v>已完成</v>
       </c>
     </row>
     <row r="14">
@@ -873,32 +717,31 @@
         <v>五、后续迭代</v>
       </c>
       <c r="C14" t="str">
-        <v>迭代点（可选）</v>
+        <v>迭代点（已全部落地，U3-11）</v>
       </c>
       <c r="D14" t="str">
-        <v>① 空段抽样人工复核入口；② 分块重叠窗口可调；③ 纯设定类长文自动跳过分幕；④ 纠偏提示按世界类型微调</v>
+        <v>① 空段复核入口：分幕视图显示空段提示 +「复核空段」按钮，复用补跑机制只对空段强制再分一次；② 分块长度/重叠可调：设置页「AI 长文本解析参数」卡片，留空/越界回落默认，补跑时强制默认保证段边界对齐；③ 纯设定类长文自动跳过分幕：全文≥4000 字且无任何叙事信号时跳过并说明原因（设置可关闭，非中文不跳过）；④ 纠偏提示按世界观微调：两条链路的空结果纠偏尾注拼装当前团名</v>
       </c>
       <c r="E14" t="str">
-        <v>迭代清单</v>
+        <v>U3-11 回归 GREEN；npm test 458 pass / 0 fail</v>
       </c>
       <c r="F14" t="str">
-        <v>下一版本评估</v>
+        <v>行为断言 + 结构断言全覆盖</v>
       </c>
       <c r="G14" t="str">
-        <v>规划中</v>
+        <v>已实现</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
   </ignoredErrors>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -956,7 +799,7 @@
         <v>切分</v>
       </c>
       <c r="C4" t="str">
-        <v>结构感知切分：优先按章节标题/明显分隔切大段，再按长度上限切小块，块间保留少量重叠</v>
+        <v>结构感知切分：优先按章节标题/明显分隔切大段，再按长度上限切小块，块间保留少量重叠；块长/重叠可在设置微调（补跑时强制默认保证段边界对齐）</v>
       </c>
       <c r="D4" t="str">
         <v>避免把完整剧情节点拦腰斩断，降低上下文断裂</v>
@@ -967,13 +810,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>链路A·取卡</v>
+        <v>分幕预检</v>
       </c>
       <c r="C5" t="str">
-        <v>逐块拆分登记：每块调用 registration 场景，输出 7 类实体（pcs/npcs/regions/logs/mobs/rules/lore）</v>
+        <v>纯设定类长文自动跳过分幕：全文≥4000 字且连一条叙事信号（对话/称呼/场景推进）都没有时，直接说明原因并跳过 AI 调用（设置可关闭；非中文文本不跳过）</v>
       </c>
       <c r="D5" t="str">
-        <v>分而治之：控制单次 token，同时保住提取粒度</v>
+        <v>设定/规则/目录类内容分幕必然产出空幕——省下整次白跑的 token 与等待；判据放宽防误跳</v>
       </c>
     </row>
     <row r="6">
@@ -984,10 +827,10 @@
         <v>链路A·取卡</v>
       </c>
       <c r="C6" t="str">
-        <v>空结果质量闸：空结果 → hasEntitySignals 预检 → 有信号则注入纠偏尾注重试 1 次 → 仍空则记 emptyIdx</v>
+        <v>逐块拆分登记：每块调用 registration 场景，输出 7 类实体（pcs/npcs/regions/logs/mobs/rules/lore）</v>
       </c>
       <c r="D6" t="str">
-        <v>把 token 花在"本该有产出却偷懒"的块上，而不是无脑重试</v>
+        <v>分而治之：控制单次 token，同时保住提取粒度</v>
       </c>
     </row>
     <row r="7">
@@ -998,10 +841,10 @@
         <v>链路A·取卡</v>
       </c>
       <c r="C7" t="str">
-        <v>跨块合并：按 name/title 归并同名实体，冲突与合并建议写入 updates</v>
+        <v>空结果质量闸：空结果 → hasEntitySignals 预检 → 有信号则注入纠偏尾注（附当前团名做世界观微调）重试 1 次 → 仍空则记 emptyIdx</v>
       </c>
       <c r="D7" t="str">
-        <v>长文实体分散在多块，合并才能还原全貌</v>
+        <v>把 token 花在"本该有产出却偷懒"的块上，而不是无脑重试</v>
       </c>
     </row>
     <row r="8">
@@ -1009,13 +852,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>链路B·分幕</v>
+        <v>链路A·取卡</v>
       </c>
       <c r="C8" t="str">
-        <v>逐块分幕：每块调用 scenario 场景输出结构化幕；续块使用精简系统提示 + 跨段滚动锚点（上幕结尾作为承接）</v>
+        <v>跨块合并：按 name/title 归并同名实体，冲突与合并建议写入 updates</v>
       </c>
       <c r="D8" t="str">
-        <v>锚点省 token 又保剧情连贯；细则保留保证分幕质量</v>
+        <v>长文实体分散在多块，合并才能还原全貌</v>
       </c>
     </row>
     <row r="9">
@@ -1026,10 +869,10 @@
         <v>链路B·分幕</v>
       </c>
       <c r="C9" t="str">
-        <v>空结果质量闸：空 scenes → 同 Sheet1 第 9 条质量闸</v>
+        <v>逐块分幕：每块调用 scenario 场景输出结构化幕；续块使用精简系统提示 + 跨段滚动锚点（上幕结尾作为承接）</v>
       </c>
       <c r="D9" t="str">
-        <v>同取卡链路，保证两链路质量一致</v>
+        <v>锚点省 token 又保剧情连贯；细则保留保证分幕质量</v>
       </c>
     </row>
     <row r="10">
@@ -1037,13 +880,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>补尾</v>
+        <v>链路B·分幕</v>
       </c>
       <c r="C10" t="str">
-        <v>续写补尾：末块疑似截断时触发一次续写补尾</v>
+        <v>空结果质量闸：空 scenes → 同取卡链路的质量闸（信号预检 + 世界观微调纠偏重试 1 次 → 仍空记 emptyIdx）</v>
       </c>
       <c r="D10" t="str">
-        <v>防止切分把结尾剧情丢掉</v>
+        <v>两条链路质量一致，空段可追溯</v>
       </c>
     </row>
     <row r="11">
@@ -1051,13 +894,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>汇总</v>
+        <v>补尾</v>
       </c>
       <c r="C11" t="str">
-        <v>输出与告警：scenes 顺序拼接 + 实体合并 + 空段清单写入告警</v>
+        <v>续写补尾：末块疑似截断时触发一次续写补尾</v>
       </c>
       <c r="D11" t="str">
-        <v>失败透明化：用户知道哪些段需要人工处理</v>
+        <v>防止切分把结尾剧情丢掉</v>
       </c>
     </row>
     <row r="12">
@@ -1065,20 +908,33 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
+        <v>汇总</v>
+      </c>
+      <c r="C12" t="str">
+        <v>输出与告警：scenes 顺序拼接 + 实体合并 + 空段清单回传渲染层——分幕视图提供「复核空段」入口，复用补跑机制只对空段强制再分</v>
+      </c>
+      <c r="D12" t="str">
+        <v>失败透明化 + 可操作补救路径：用户知道哪些段需要人工处理</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
         <v>验证</v>
       </c>
-      <c r="C12" t="str">
-        <v>质量验收：U3-9 回归断言 + 人工抽检长文样本</v>
-      </c>
-      <c r="D12" t="str">
+      <c r="C13" t="str">
+        <v>质量验收：U3-9/U3-11 回归断言 + 人工抽检长文样本</v>
+      </c>
+      <c r="D13" t="str">
         <v>防回归 + 保效果</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1118,7 +974,7 @@
         <v>空结果合法化后无纠偏，模型对平淡叙事块偷懒</v>
       </c>
       <c r="C2" t="str">
-        <v>hasEntitySignals 本地预检 + EMPTY_SEG_NUDGE 定向纠偏重试 1 次</v>
+        <v>hasEntitySignals 本地预检 + EMPTY_SEG_NUDGE 定向纠偏重试 1 次（尾注附当前团名做世界观微调）</v>
       </c>
       <c r="D2" t="str">
         <v>U3-9 断言</v>
@@ -1152,10 +1008,10 @@
         <v>空结果静默放行、无记录</v>
       </c>
       <c r="C4" t="str">
-        <v>emptyIdx 记录 + 告警写明空段说明</v>
+        <v>emptyIdx 记录 + 告警写明空段说明 + 分幕视图「复核空段」按钮（复用补跑机制强制再分）</v>
       </c>
       <c r="D4" t="str">
-        <v>U3-9 断言 + 告警文案</v>
+        <v>U3-9/U3-11 断言</v>
       </c>
       <c r="E4" t="str">
         <v>已修复</v>
@@ -1169,10 +1025,10 @@
         <v>旧版对空结果无脑多轮重试</v>
       </c>
       <c r="C5" t="str">
-        <v>纠偏重试严格限 1 次，且仅对命中信号者触发（预检本身零 token）</v>
+        <v>纠偏重试严格限 1 次，且仅对命中信号者触发（预检本身零 token）；纯设定类长文整篇直接跳过分幕</v>
       </c>
       <c r="D5" t="str">
-        <v>U3-9 断言重试次数</v>
+        <v>U3-9/U3-11 断言</v>
       </c>
       <c r="E5" t="str">
         <v>已修复</v>
@@ -1182,6 +1038,5 @@
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>